--- a/hpm_sdk/samples/ethercat/ecat_io/SSC/digital_io.xlsx
+++ b/hpm_sdk/samples/ethercat/ecat_io/SSC/digital_io.xlsx
@@ -1,41 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EtherCAT\SSC config\0130\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\QIAN\Documents\GitHub\asyncmc\library\hpm_sdk_env\hpm_sdk\samples\ethercat\ecat_io\SSC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCC0E51C-2308-44A2-B724-6232A3D41C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2620A3F-B4F2-4790-82E0-16FD5C06C684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1410" yWindow="5010" windowWidth="18720" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25800" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Profile" sheetId="11" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$51</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Profile!$B$10:$P$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Profile!$B$1:$P$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="82">
   <si>
     <t>Index</t>
   </si>
@@ -331,16 +320,9 @@
     <t>PdoIndexIncrement:</t>
   </si>
   <si>
-    <t>0x6000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>VARIABLE</t>
   </si>
   <si>
-    <t>InputCounter</t>
-  </si>
-  <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -369,6 +351,62 @@
   </si>
   <si>
     <t>rx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x6403</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Voltage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x6413</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Current</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x6120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>InputBits</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x6423</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>VARIABLE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>REAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Temperature</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -504,9 +542,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -544,9 +582,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -579,26 +617,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -631,26 +652,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -824,26 +828,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:T55"/>
-  <sheetFormatPr defaultColWidth="10.7265625" defaultRowHeight="14" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:T57"/>
+  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="13.5" outlineLevelRow="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="3.81640625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.26953125" style="2" customWidth="1"/>
-    <col min="3" max="5" width="14.7265625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="40.7265625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.7265625" style="2" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.26953125" style="2" customWidth="1"/>
-    <col min="11" max="11" width="7.7265625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="11.7265625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="7.7265625" style="2" customWidth="1"/>
-    <col min="14" max="14" width="11.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.81640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="35.7265625" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="10.7265625" style="2"/>
+    <col min="1" max="1" width="3.875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="2" customWidth="1"/>
+    <col min="3" max="5" width="14.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="40.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="7.75" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="7.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="11.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="7.75" style="2" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="35.75" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="10.75" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:20" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" t="s">
         <v>15</v>
       </c>
@@ -872,7 +876,7 @@
       <c r="S1" s="12"/>
       <c r="T1" s="12"/>
     </row>
-    <row r="2" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B2" t="s">
         <v>17</v>
       </c>
@@ -896,7 +900,7 @@
       <c r="S2" s="12"/>
       <c r="T2" s="12"/>
     </row>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B3" s="15" t="s">
         <v>57</v>
       </c>
@@ -921,7 +925,7 @@
       <c r="S3" s="12"/>
       <c r="T3" s="12"/>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B4" t="s">
         <v>58</v>
       </c>
@@ -946,7 +950,7 @@
       <c r="S4" s="12"/>
       <c r="T4" s="12"/>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
@@ -967,7 +971,7 @@
       <c r="S5" s="12"/>
       <c r="T5" s="12"/>
     </row>
-    <row r="6" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B6"/>
       <c r="C6"/>
       <c r="D6"/>
@@ -988,7 +992,7 @@
       <c r="S6" s="12"/>
       <c r="T6" s="12"/>
     </row>
-    <row r="7" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B7"/>
       <c r="C7"/>
       <c r="D7"/>
@@ -1009,7 +1013,7 @@
       <c r="S7" s="12"/>
       <c r="T7" s="12"/>
     </row>
-    <row r="8" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1028,7 +1032,7 @@
       <c r="O8"/>
       <c r="P8"/>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B9"/>
       <c r="C9"/>
       <c r="D9"/>
@@ -1045,7 +1049,7 @@
       <c r="O9"/>
       <c r="P9"/>
     </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B10" s="6" t="s">
         <v>0</v>
       </c>
@@ -1092,7 +1096,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="2:20" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:20" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B11" s="11" t="s">
         <v>19</v>
       </c>
@@ -1113,7 +1117,7 @@
       <c r="O11" s="11"/>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:20" x14ac:dyDescent="0.15">
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12" s="7"/>
@@ -1130,7 +1134,7 @@
       <c r="O12"/>
       <c r="P12"/>
     </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D13" s="8"/>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
@@ -1141,7 +1145,7 @@
       <c r="O13"/>
       <c r="P13"/>
     </row>
-    <row r="14" spans="2:20" s="10" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:20" s="10" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B14" s="11" t="s">
         <v>32</v>
       </c>
@@ -1162,7 +1166,7 @@
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
     </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D15" s="8"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
@@ -1173,7 +1177,7 @@
       <c r="O15"/>
       <c r="P15"/>
     </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:20" x14ac:dyDescent="0.15">
       <c r="D16" s="8"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
@@ -1184,7 +1188,7 @@
       <c r="O16"/>
       <c r="P16"/>
     </row>
-    <row r="17" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="B17" s="11" t="s">
         <v>21</v>
       </c>
@@ -1205,7 +1209,7 @@
       <c r="O17" s="11"/>
       <c r="P17" s="11"/>
     </row>
-    <row r="18" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D18" s="8"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
@@ -1216,7 +1220,7 @@
       <c r="O18"/>
       <c r="P18"/>
     </row>
-    <row r="19" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D19" s="8"/>
       <c r="E19" s="10"/>
       <c r="F19" s="10"/>
@@ -1227,7 +1231,7 @@
       <c r="O19"/>
       <c r="P19"/>
     </row>
-    <row r="20" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="B20" s="11" t="s">
         <v>23</v>
       </c>
@@ -1248,7 +1252,7 @@
       <c r="O20" s="11"/>
       <c r="P20" s="11"/>
     </row>
-    <row r="21" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D21" s="8"/>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
@@ -1259,7 +1263,7 @@
       <c r="O21"/>
       <c r="P21"/>
     </row>
-    <row r="22" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D22" s="8"/>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
@@ -1270,7 +1274,7 @@
       <c r="O22"/>
       <c r="P22"/>
     </row>
-    <row r="23" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="B23" s="11" t="s">
         <v>24</v>
       </c>
@@ -1291,7 +1295,7 @@
       <c r="O23" s="11"/>
       <c r="P23" s="11"/>
     </row>
-    <row r="24" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D24" s="8"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
@@ -1302,7 +1306,7 @@
       <c r="O24"/>
       <c r="P24"/>
     </row>
-    <row r="25" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D25" s="8"/>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
@@ -1313,7 +1317,7 @@
       <c r="O25"/>
       <c r="P25"/>
     </row>
-    <row r="26" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="B26" s="11" t="s">
         <v>26</v>
       </c>
@@ -1334,7 +1338,7 @@
       <c r="O26" s="11"/>
       <c r="P26" s="11"/>
     </row>
-    <row r="27" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D27" s="8"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
@@ -1345,7 +1349,7 @@
       <c r="O27"/>
       <c r="P27"/>
     </row>
-    <row r="28" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D28" s="8"/>
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
@@ -1356,7 +1360,7 @@
       <c r="O28"/>
       <c r="P28"/>
     </row>
-    <row r="29" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="B29" s="11" t="s">
         <v>34</v>
       </c>
@@ -1377,7 +1381,7 @@
       <c r="O29" s="11"/>
       <c r="P29" s="11"/>
     </row>
-    <row r="30" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D30" s="8"/>
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
@@ -1388,7 +1392,7 @@
       <c r="O30"/>
       <c r="P30"/>
     </row>
-    <row r="31" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D31" s="8"/>
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
@@ -1399,7 +1403,7 @@
       <c r="O31"/>
       <c r="P31"/>
     </row>
-    <row r="32" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" s="10" customFormat="1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="B32" s="11" t="s">
         <v>35</v>
       </c>
@@ -1420,7 +1424,7 @@
       <c r="O32" s="11"/>
       <c r="P32" s="11"/>
     </row>
-    <row r="33" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D33" s="8"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
@@ -1431,7 +1435,7 @@
       <c r="O33"/>
       <c r="P33"/>
     </row>
-    <row r="34" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="D34" s="8"/>
       <c r="E34" s="10"/>
       <c r="F34" s="10"/>
@@ -1442,7 +1446,7 @@
       <c r="O34"/>
       <c r="P34"/>
     </row>
-    <row r="35" spans="2:16" s="10" customFormat="1" collapsed="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" s="10" customFormat="1" collapsed="1" x14ac:dyDescent="0.15">
       <c r="B35" s="11" t="s">
         <v>20</v>
       </c>
@@ -1463,129 +1467,173 @@
       <c r="O35" s="11"/>
       <c r="P35" s="11"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B36" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>60</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F36" s="10" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H36" s="10"/>
       <c r="I36" s="10"/>
       <c r="L36" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N36"/>
       <c r="O36"/>
       <c r="P36"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B37" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="D37" s="8"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+      <c r="E37" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>71</v>
+      </c>
       <c r="H37" s="10"/>
       <c r="I37" s="10"/>
+      <c r="L37" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>73</v>
+      </c>
       <c r="N37"/>
       <c r="O37"/>
       <c r="P37"/>
     </row>
-    <row r="38" spans="2:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D38" s="11"/>
-      <c r="E38" s="11"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="11"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B38" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D38" s="8"/>
+      <c r="E38" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="L38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="10" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H39" s="10"/>
       <c r="I39" s="10"/>
       <c r="L39" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="N39"/>
       <c r="O39"/>
       <c r="P39"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D40" s="8"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="10"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
-      <c r="I40" s="10"/>
-      <c r="N40"/>
-      <c r="O40"/>
-      <c r="P40"/>
-    </row>
-    <row r="41" spans="2:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D41" s="11"/>
-      <c r="E41" s="11"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="11"/>
+      <c r="L40" s="11"/>
+      <c r="M40" s="11"/>
+      <c r="N40" s="11"/>
+      <c r="O40" s="11"/>
+      <c r="P40" s="11"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B41" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="8"/>
+      <c r="E41" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H41" s="10"/>
+      <c r="I41" s="10"/>
+      <c r="L41" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.15">
       <c r="D42" s="8"/>
       <c r="E42" s="10"/>
       <c r="F42" s="10"/>
@@ -1596,39 +1644,39 @@
       <c r="O42"/>
       <c r="P42"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D43" s="8"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="10"/>
-      <c r="N43"/>
-      <c r="O43"/>
-      <c r="P43"/>
-    </row>
-    <row r="44" spans="2:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="D44" s="8"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.15">
       <c r="D45" s="8"/>
       <c r="E45" s="10"/>
       <c r="F45" s="10"/>
@@ -1639,39 +1687,39 @@
       <c r="O45"/>
       <c r="P45"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D46" s="8"/>
-      <c r="E46" s="10"/>
-      <c r="F46" s="10"/>
-      <c r="G46" s="10"/>
-      <c r="H46" s="10"/>
-      <c r="I46" s="10"/>
-      <c r="N46"/>
-      <c r="O46"/>
-      <c r="P46"/>
-    </row>
-    <row r="47" spans="2:16" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="11"/>
-      <c r="G47" s="11"/>
-      <c r="H47" s="11"/>
-      <c r="I47" s="11"/>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B46" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
+      <c r="M46" s="11"/>
+      <c r="N46" s="11"/>
+      <c r="O46" s="11"/>
+      <c r="P46" s="11"/>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="D47" s="8"/>
+      <c r="E47" s="10"/>
+      <c r="F47" s="10"/>
+      <c r="G47" s="10"/>
+      <c r="H47" s="10"/>
+      <c r="I47" s="10"/>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.15">
       <c r="D48" s="8"/>
       <c r="E48" s="10"/>
       <c r="F48" s="10"/>
@@ -1682,103 +1730,81 @@
       <c r="O48"/>
       <c r="P48"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="D49" s="8"/>
-      <c r="E49" s="10"/>
-      <c r="F49" s="10"/>
-      <c r="G49" s="10"/>
-      <c r="H49" s="10"/>
-      <c r="I49" s="10"/>
-      <c r="N49"/>
-      <c r="O49"/>
-      <c r="P49"/>
-    </row>
-    <row r="50" spans="2:16" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="13"/>
-      <c r="H50" s="13"/>
-      <c r="I50" s="13"/>
-      <c r="J50" s="13"/>
-      <c r="K50" s="13"/>
-      <c r="L50" s="13"/>
-      <c r="M50" s="13"/>
-      <c r="N50" s="13"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
-    </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" t="s">
-        <v>47</v>
-      </c>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51" t="s">
-        <v>16</v>
-      </c>
-      <c r="G51"/>
-      <c r="H51"/>
-      <c r="I51"/>
-      <c r="J51" t="s">
-        <v>48</v>
-      </c>
-      <c r="K51"/>
-      <c r="L51"/>
-      <c r="M51"/>
+    <row r="49" spans="2:16" s="10" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B49" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+      <c r="K49" s="11"/>
+      <c r="L49" s="11"/>
+      <c r="M49" s="11"/>
+      <c r="N49" s="11"/>
+      <c r="O49" s="11"/>
+      <c r="P49" s="11"/>
+    </row>
+    <row r="50" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="D50" s="8"/>
+      <c r="E50" s="10"/>
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="N50"/>
+      <c r="O50"/>
+      <c r="P50"/>
+    </row>
+    <row r="51" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="D51" s="8"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
       <c r="N51"/>
       <c r="O51"/>
       <c r="P51"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52" t="s">
-        <v>49</v>
-      </c>
-      <c r="F52" t="s">
-        <v>50</v>
-      </c>
-      <c r="G52" t="s">
-        <v>53</v>
-      </c>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52" t="s">
-        <v>48</v>
-      </c>
-      <c r="K52"/>
-      <c r="L52" t="s">
-        <v>51</v>
-      </c>
-      <c r="M52"/>
-      <c r="N52" s="14"/>
-      <c r="O52"/>
-      <c r="P52"/>
-    </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53">
-        <v>2</v>
-      </c>
-      <c r="E53" t="s">
-        <v>49</v>
-      </c>
+    <row r="52" spans="2:16" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="11"/>
+    </row>
+    <row r="53" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" t="s">
+        <v>47</v>
+      </c>
+      <c r="D53"/>
+      <c r="E53"/>
       <c r="F53" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="G53"/>
       <c r="H53"/>
@@ -1787,64 +1813,118 @@
         <v>48</v>
       </c>
       <c r="K53"/>
-      <c r="L53" t="s">
-        <v>51</v>
-      </c>
+      <c r="L53"/>
       <c r="M53"/>
       <c r="N53"/>
-    </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O53"/>
+      <c r="P53"/>
+    </row>
+    <row r="54" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B54"/>
       <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" t="s">
+        <v>53</v>
+      </c>
       <c r="H54"/>
       <c r="I54"/>
-      <c r="J54"/>
+      <c r="J54" t="s">
+        <v>48</v>
+      </c>
       <c r="K54"/>
-      <c r="L54"/>
+      <c r="L54" t="s">
+        <v>51</v>
+      </c>
       <c r="M54"/>
       <c r="N54" s="14"/>
-    </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="O54"/>
+      <c r="P54"/>
+    </row>
+    <row r="55" spans="2:16" x14ac:dyDescent="0.15">
       <c r="B55"/>
       <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
+      <c r="D55">
+        <v>2</v>
+      </c>
+      <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" t="s">
+        <v>52</v>
+      </c>
       <c r="G55"/>
       <c r="H55"/>
       <c r="I55"/>
-      <c r="J55"/>
+      <c r="J55" t="s">
+        <v>48</v>
+      </c>
       <c r="K55"/>
-      <c r="L55"/>
+      <c r="L55" t="s">
+        <v>51</v>
+      </c>
       <c r="M55"/>
       <c r="N55"/>
     </row>
+    <row r="56" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56"/>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56" s="14"/>
+    </row>
+    <row r="57" spans="2:16" x14ac:dyDescent="0.15">
+      <c r="B57"/>
+      <c r="C57"/>
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatRows="0" insertRows="0" insertHyperlinks="0" deleteRows="0" sort="0" autoFilter="0"/>
-  <autoFilter ref="B10:P51" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="B10:P53" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="F1:P6"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C63:C902" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C65:C904" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M15:M16 M18:M19 M21:M22 M27:M28 M30:M31 M33:M34 M12:M13 M42:M43 M45:M46 M48:M51 M24:M25 M36:M37 M39:M40" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M15:M16 M18:M19 M21:M22 M27:M28 M30:M31 M33:M34 M12:M13 M44:M45 M47:M48 M50:M53 M24:M25 M41:M42 M36:M39" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"rx,tx"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C27:C28 C30:C31 C33:C34 C36:C37 C42:C43 C45:C46 C48:C62 C24:C25 C39:C40" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Object Code value" error="The Object code value shall be:_x000a_VARIABLE_x000a_RECORD_x000a_ARRAY" sqref="C12:C13 C15:C16 C18:C19 C21:C22 C27:C28 C30:C31 C33:C34 C41:C42 C44:C45 C47:C48 C50:C64 C24:C25 C36:C39" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"VARIABLE,ARRAY,RECORD"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C38 C41 C44 C47" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J27:J28 J30:J31 J33:J34 J36:J37 J42:J43 J45:J46 J48:J62 J24:J25 J39:J40" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation allowBlank="1" showInputMessage="1" sqref="C11 C14 C17 C20 C23 C26 C29 C32 C35 C40 C43 C46 C49" xr:uid="{00000000-0002-0000-0000-000003000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Category" error="The value for the entry category shall be _x000a_M : (mandatory)_x000a_O : (optional) _x000a_C : (conditional)" sqref="J12:J13 J15:J16 J18:J19 J21:J22 J27:J28 J30:J31 J33:J34 J41:J42 J44:J45 J47:J48 J50:J64 J24:J25 J36:J39" xr:uid="{00000000-0002-0000-0000-000004000000}">
       <formula1>"M,O,C"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K27:K28 K30:K31 K33:K34 K36:K37 K42:K43 K45:K46 K48:K62 K24:K25 K39:K40" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Backup/Setting Flag" error="The entry flag shall be_x000a_B : (Backup)_x000a_S : (Setting)" sqref="K12:K13 K15:K16 K18:K19 K21:K22 K27:K28 K30:K31 K33:K34 K41:K42 K44:K45 K47:K48 K50:K64 K24:K25 K36:K39" xr:uid="{00000000-0002-0000-0000-000005000000}">
       <formula1>"B,S"</formula1>
     </dataValidation>
   </dataValidations>
